--- a/output/topology_excel/13762.xlsx
+++ b/output/topology_excel/13762.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -520,15 +520,15 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
         <v>8</v>
@@ -542,7 +542,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,15 +586,15 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
         <v>8</v>
@@ -616,7 +616,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
         <v>9</v>
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F9" t="n">
         <v>9</v>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,29 +652,29 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="F11" t="n">
         <v>38</v>
@@ -682,24 +682,24 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
         <v>4</v>
       </c>
-      <c r="B12" t="n">
-        <v>11</v>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Wall</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -795,7 +795,7 @@
         <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>171</v>
+        <v>377</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -817,7 +817,7 @@
         <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>419</v>
+        <v>171</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,15 +938,15 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F23" t="n">
-        <v>156</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" t="n">
         <v>8</v>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>195</v>
+        <v>146</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>115</v>
+        <v>374</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,18 +1004,18 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>301</v>
+        <v>115</v>
       </c>
       <c r="F26" t="n">
-        <v>153</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -1037,7 +1037,7 @@
         <v>6</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1051,15 +1051,15 @@
         <v>182</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>374</v>
+        <v>182</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,18 +1092,18 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,10 +1114,142 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
+        <v>134</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>195</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" t="n">
+        <v>9</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>292</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
         <v>244</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F34" t="n">
         <v>38</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>390</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>125</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/13762.xlsx
+++ b/output/topology_excel/13762.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>171</v>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -853,7 +853,7 @@
         <v>159</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
